--- a/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clément marche avec maman. Ils vont au parc. Le vent est doux. Ils sentent les feuilles. Ils arrivent au bord. Le bord du trottoir est là. Maman s'arrête. Clément s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clément sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman dit : on s'arrête. Pieds au bord. Sur le trottoir. Clément regarde maman. Il pose les pieds au bord. Les pieds sont calmes. Maman sourit. Maman dit : bravo Clément. On s'arrête au trottoir. On attend avec maman. Les pieds restent au bord du trottoir.</t>
+          <t>Clément marche avec maman. Ils vont au parc. Le vent est doux. Ils sentent les feuilles. Ils arrivent au bord. Le bord du trottoir est là. Maman s'arrête. Clément s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clément sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Clément regarde maman. Il pose les pieds au bord. Les pieds sont calmes. Maman sourit. Bravo Clément. On s'arrête au trottoir. On attend avec maman. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clément marche avec maman. Ils vont au parc. Le vent est doux. Ils sentent les feuilles. Ils arrivent au bord. Le bord du trottoir est là. Maman s'arrête. Clément s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clément sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
+maman|On s'arrête. Pieds au bord. Sur le trottoir.
+narrateur|Clément regarde maman. Il pose les pieds au bord. Les pieds sont calmes. Maman sourit.
+maman|Bravo Clément. On s'arrête au trottoir. On attend avec maman.
+narrateur|Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Clément arrive au bord. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Clément s'arrête au bord. Les pieds sont sur le trottoir. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Clément donne la main à maman. Ils attendent un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Clément arrive au bord. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Clément s'arrête au bord. Les pieds sont sur le trottoir. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1859,7 @@
           <t>narrateur|Clément donne la main à maman. Ils attendent un moment.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clément s'arrête au trottoir</t>
+          <t>Les bottes rouges de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une feuille jaune colle à la vitre. Nino et maman vont au parc. La balle est dans le sac. Au bord, Nino s'arrête. Pieds au bord, sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clément marche avec maman. Ils vont au parc. Le vent est doux. Ils sentent les feuilles. Ils arrivent au bord. Le bord du trottoir est là. Maman s'arrête. Clément s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clément sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Clément regarde maman. Il pose les pieds au bord. Les pieds sont calmes. Maman sourit. Bravo Clément. On s'arrête au trottoir. On attend avec maman. Les pieds restent au bord du trottoir.</t>
+          <t>Une feuille jaune colle à la vitre. Elle est un peu froissée, toute sèche. Le vent la fait trembler. Les bottes rouges attendent près de la porte. Elles brillent, encore un peu humides. Un sac souple tient une balle bleue. La balle sent le caoutchouc. Nino vit ici, avec maman. Maman, la feuille tremble ! Oui. Le vent est doux. Tu mets tes bottes ? En ce moment, Nino s'assoit. Il enfile la botte gauche. Puis la botte droite. Le caoutchouc fait un petit ploc. Tu as fini tes bottes ? Oui, maman. Bravo. On prend la balle. Maman ouvre la porte. L'air sent les feuilles mouillées. Ça sent le parc ! Oui. On marche sur le trottoir. Nino donne la main à maman. Les bottes tapent un rythme doux. Une feuille sèche crisse sous une botte. Le sac souple tape contre la jambe. La balle est dedans ? Oui. On reste sur le trottoir. Les arbres du parc sont plus près. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Nino s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le vent touche les joues de Nino. Les bottes rouges restent bien posées. Bravo, Nino. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Clément marche avec maman. Ils vont au parc. Le vent est doux. Ils sentent les feuilles. Ils arrivent au bord. Le bord du trottoir est là. Maman s'arrête. Clément s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clément sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
-maman|On s'arrête. Pieds au bord. Sur le trottoir.
-narrateur|Clément regarde maman. Il pose les pieds au bord. Les pieds sont calmes. Maman sourit.
-maman|Bravo Clément. On s'arrête au trottoir. On attend avec maman.
+          <t>narrateur|Une feuille jaune colle à la vitre.
+narrateur|Elle est un peu froissée, toute sèche.
+narrateur|Le vent la fait trembler.
+narrateur|Les bottes rouges attendent près de la porte.
+narrateur|Elles brillent, encore un peu humides.
+narrateur|Un sac souple tient une balle bleue.
+narrateur|La balle sent le caoutchouc.
+narrateur|Nino vit ici, avec maman.
+enfant-m|Maman, la feuille tremble !
+maman|Oui.
+maman|Le vent est doux.
+maman|Tu mets tes bottes ?
+narrateur|En ce moment, Nino s'assoit.
+narrateur|Il enfile la botte gauche.
+narrateur|Puis la botte droite.
+narrateur|Le caoutchouc fait un petit ploc.
+maman|Tu as fini tes bottes ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|On prend la balle.
+narrateur|Maman ouvre la porte.
+narrateur|L'air sent les feuilles mouillées.
+enfant-m|Ça sent le parc !
+maman|Oui.
+maman|On marche sur le trottoir.
+narrateur|Nino donne la main à maman.
+narrateur|Les bottes tapent un rythme doux.
+narrateur|Une feuille sèche crisse sous une botte.
+narrateur|Le sac souple tape contre la jambe.
+enfant-m|La balle est dedans ?
+maman|Oui.
+maman|On reste sur le trottoir.
+narrateur|Les arbres du parc sont plus près.
+narrateur|Le bord du trottoir arrive.
+narrateur|Le bord est gris et net.
+maman|On va s'arrêter.
+maman|Pieds au bord.
+maman|Sur le trottoir.
+narrateur|Nino s'arrête.
+narrateur|Ses pieds sont au bord.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+enfant-m|Je m'arrête.
+maman|Oui.
+maman|On attend avec maman.
+maman|Tes pieds sont calmes ?
+enfant-m|Oui.
+narrateur|Le vent touche les joues de Nino.
+narrateur|Les bottes rouges restent bien posées.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
@@ -1348,7 +1407,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Clément arrive au bord. Que fait-il ?</t>
+          <t>Nino arrive au bord. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Clément arrive au bord. Que fait-il ?</t>
+          <t>narrateur|Nino arrive au bord.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Clément s'arrête au bord. Les pieds sont sur le trottoir. Maman est là.</t>
+          <t>Nino s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Nino. On attend avec maman. La main de maman est chaude. Les bottes rouges sont un peu froides. Le vent bouge encore la feuille.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1744,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Clément s'arrête au bord. Les pieds sont sur le trottoir. Maman est là.</t>
+          <t>narrateur|Nino s'arrête au bord.
+narrateur|Les pieds sont sur le trottoir.
+narrateur|Les pieds restent au bord.
+maman|Tu t'arrêtes au trottoir ?
+enfant-m|Oui.
+enfant-m|Je m'arrête.
+maman|Bravo, Nino.
+maman|On attend avec maman.
+narrateur|La main de maman est chaude.
+narrateur|Les bottes rouges sont un peu froides.
+narrateur|Le vent bouge encore la feuille.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Clément donne la main à maman. Ils attendent un moment.</t>
+          <t>On y va ensemble ? Oui, maman. Ils marchent avec l'adulte. Le parc sent l'herbe. La balle bleue sort du sac. Tu la lances ? Nino lance la balle. Elle fait un petit ploc. Elle rebondit ! Oui. Tu as fini de lancer ? Oui. Bravo. Les bottes rouges brillent dans l'herbe. Une feuille jaune vole encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1856,10 +1926,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Clément donne la main à maman. Ils attendent un moment.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>maman|On y va ensemble ?
+enfant-m|Oui, maman.
+narrateur|Ils marchent avec l'adulte.
+narrateur|Le parc sent l'herbe.
+narrateur|La balle bleue sort du sac.
+maman|Tu la lances ?
+narrateur|Nino lance la balle.
+narrateur|Elle fait un petit ploc.
+enfant-m|Elle rebondit !
+maman|Oui.
+maman|Tu as fini de lancer ?
+enfant-m|Oui.
+maman|Bravo.
+narrateur|Les bottes rouges brillent dans l'herbe.
+narrateur|Une feuille jaune vole encore.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1884,7 +1972,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Nino. La balle bleue dort dans l'herbe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2024,7 +2112,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je me suis arrêté.
+maman|Pieds au bord.
+maman|Sur le trottoir.
+maman|Bravo, Nino.
+narrateur|La balle bleue dort dans l'herbe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2046,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2177,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille jaune colle à la vitre. Elle est un peu froissée, toute sèche. Le vent la fait trembler. Les bottes rouges attendent près de la porte. Elles brillent, encore un peu humides. Un sac souple tient une balle bleue. La balle sent le caoutchouc. Nino vit ici, avec maman. Maman, la feuille tremble ! Oui. Le vent est doux. Tu mets tes bottes ? En ce moment, Nino s'assoit. Il enfile la botte gauche. Puis la botte droite. Le caoutchouc fait un petit ploc. Tu as fini tes bottes ? Oui, maman. Bravo. On prend la balle. Maman ouvre la porte. L'air sent les feuilles mouillées. Ça sent le parc ! Oui. On marche sur le trottoir. Nino donne la main à maman. Les bottes tapent un rythme doux. Une feuille sèche crisse sous une botte. Le sac souple tape contre la jambe. La balle est dedans ? Oui. On reste sur le trottoir. Les arbres du parc sont plus près. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Nino s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le vent touche les joues de Nino. Les bottes rouges restent bien posées. Bravo, Nino. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
+          <t>Une feuille jaune colle à la vitre. Elle est un peu froissée, toute sèche. Le vent la fait trembler. Les bottes rouges attendent près de la porte. Elles brillent, encore un peu humides. Un sac souple tient une balle bleue. La balle sent le caoutchouc. Nino vit ici, avec maman. Maman, la feuille tremble ! Oui. Le vent est doux. Tu mets tes bottes ? En ce moment, Nino s'assoit. Il enfile la botte gauche. Puis la botte droite. Le caoutchouc fait un petit ploc. Tu as fini tes bottes ? Oui, maman. Bravo. On prend la balle. Maman ouvre la porte. L'air sent les feuilles mouillées. Ça sent le parc ! Oui. On marche sur le trottoir. Nino donne la main à maman. Les bottes tapent un rythme doux. Une feuille sèche crisse sous une botte. Le sac souple tape contre la jambe. La balle est dedans ? Oui. On reste sur le trottoir. Les arbres du parc sont plus près. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Nino s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le vent touche les joues de Nino. Les bottes rouges restent bien posées. Bravo, Nino. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clément marche avec maman. Ils vont au parc. Le vent est doux. Ils sentent les feuilles. Ils arrivent au bord. Le bord du &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt; est là. Maman s'arrête. Clément s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clément sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman dit : on s'arrête. Pieds au bord. Sur le trottoir. Clément regarde maman. Il pose les pieds au bord. Les pieds sont calmes. Maman sourit. Maman dit : bravo Clément. On s'arrête au trottoir. On attend avec maman. Les pieds restent au bord du trottoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille jaune colle à la vitre. Elle est un peu froissée, toute sèche. Le vent la fait trembler. Les bottes rouges attendent près de la porte. Elles brillent, encore un peu humides. Un sac souple tient une balle bleue. La balle sent le caoutchouc. Nino vit ici, avec maman. Maman, la feuille tremble ! Oui. Le vent est doux. Tu mets tes bottes ? En ce moment, Nino s'assoit. Il enfile la botte gauche. Puis la botte droite. Le caoutchouc fait un petit ploc. Tu as fini tes bottes ? Oui, maman. Bravo. On prend la balle. Maman ouvre la porte. L'air sent les feuilles mouillées. Ça sent le parc ! Oui. On marche sur le trottoir. Nino donne la main à maman. Les bottes tapent un rythme doux. Une feuille sèche crisse sous une botte. Le sac souple tape contre la jambe. La balle est dedans ? Oui. On reste sur le trottoir. Les arbres du parc sont plus près. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Nino s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le vent touche les joues de Nino. Les bottes rouges restent bien posées. Bravo, Nino. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1374,7 +1374,6 @@
 narrateur|Le vent touche les joues de Nino.
 narrateur|Les bottes rouges restent bien posées.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
@@ -1412,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Clément arrive au bord. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino arrive au bord. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1570,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,7 +1599,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Clément s'arrête au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Nino. On attend avec maman. La main de maman est chaude. Les bottes rouges sont un peu froides. Le vent bouge encore la feuille.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1757,7 +1755,6 @@
 narrateur|Le vent bouge encore la feuille.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Clément donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à maman. Ils attendent un moment.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On y va ensemble ? Oui, maman. Ils marchent avec l'adulte. Le parc sent l'herbe. La balle bleue sort du sac. Tu la lances ? Nino lance la balle. Elle fait un petit ploc. Elle rebondit ! Oui. Tu as fini de lancer ? Oui. Bravo. Les bottes rouges brillent dans l'herbe. Une feuille jaune vole encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1972,12 +1969,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Nino. La balle bleue dort dans l'herbe. L'histoire est finie.</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Nino. La balle bleue dort dans l'herbe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Nino. La balle bleue dort dans l'herbe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2116,11 +2113,9 @@
 maman|Pieds au bord.
 maman|Sur le trottoir.
 maman|Bravo, Nino.
-narrateur|La balle bleue dort dans l'herbe.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La balle bleue dort dans l'herbe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2139,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2184,6 +2179,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers le parc</t>
+          <t>fenêtre, entrée, trottoir vers le parc</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clément, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
